--- a/real_estate_agent_forms/001_landlord_and_tenant_disclosure_form--real_estate_agent_forms.xlsx
+++ b/real_estate_agent_forms/001_landlord_and_tenant_disclosure_form--real_estate_agent_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -561,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Real Estate Agent</t>
+          <t>Real Estate Agent Forms 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Real Estate Agent</t>
+          <t>Real Estate Agent Forms 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Landlord</t>
+          <t>Landlord 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Real Estate Agent</t>
+          <t>Real Estate Agent Forms 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Landlord and Tenant</t>
+          <t>Landlord And Tenant Disclosure Form 12</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Landlord and Tenant</t>
+          <t>Landlord And Tenant Disclosure Form 13</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
